--- a/models/downapikey.xlsx
+++ b/models/downapikey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/dapi/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A160FA8-E667-DE47-A016-A408A9B6BDF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B05283-20CD-AB49-A681-EEAE4A71F268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20200" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
   <si>
     <t>name</t>
   </si>
@@ -226,10 +226,6 @@
   </si>
   <si>
     <t>id</t>
-  </si>
-  <si>
-    <t>0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>table</t>
@@ -268,26 +264,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>enabled</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>created_at</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>expires_at</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>下位系统id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>机构id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>用户id</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -296,10 +276,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>是否启用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>创建日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -336,23 +312,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>dorgid</t>
+    <t>downapikey</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>duserid</t>
+    <t>enabled_date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>下位系统机构id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>下位系统用户id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>downapikey</t>
+    <t>expired_date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -458,7 +426,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,9 +449,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -792,11 +757,11 @@
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>73</v>
+      <c r="A2" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>72</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
@@ -822,7 +787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="2" width="16.1640625" customWidth="1"/>
@@ -862,7 +827,7 @@
       <c r="A2" t="s">
         <v>66</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>66</v>
       </c>
       <c r="C2" t="s">
@@ -873,11 +838,11 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>81</v>
+      <c r="A3" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>77</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -887,11 +852,11 @@
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>97</v>
+      <c r="A4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>78</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -899,13 +864,14 @@
       <c r="D4">
         <v>32</v>
       </c>
+      <c r="F4" s="7"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="9" t="s">
-        <v>96</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>98</v>
+      <c r="A5" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>79</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -913,87 +879,27 @@
       <c r="D5">
         <v>32</v>
       </c>
+      <c r="F5" s="7"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>82</v>
+      <c r="A6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6">
         <v>32</v>
       </c>
-      <c r="G6" s="8" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>83</v>
+      <c r="A7" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7">
-        <v>32</v>
-      </c>
-      <c r="F7" s="7"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8">
-        <v>32</v>
-      </c>
-      <c r="F8" s="7"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1008,13 +914,13 @@
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
           </x14:formula1>
-          <xm:sqref>C12:C336</xm:sqref>
+          <xm:sqref>C8:C332</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00A417B3-E2E5-E542-A806-790AFA6BBECE}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C11</xm:sqref>
+          <xm:sqref>C2:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1089,62 +995,62 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="D1" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="9" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="7" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -1276,7 +1182,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="B14" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1299,14 +1205,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="11"/>
+      <c r="D1" s="10"/>
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>

--- a/models/downapikey.xlsx
+++ b/models/downapikey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/dapi/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B05283-20CD-AB49-A681-EEAE4A71F268}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78676F20-4C8D-5F43-9AB2-DA5E2AC622E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="89">
   <si>
     <t>name</t>
   </si>
@@ -252,10 +252,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>orgid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>userid</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -296,18 +292,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>organization</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>user</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>orgname</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>username</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -322,6 +306,10 @@
   <si>
     <t>expired_date</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>users</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -758,7 +746,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="8" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>72</v>
@@ -842,7 +830,7 @@
         <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C3" t="s">
         <v>10</v>
@@ -853,10 +841,10 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
@@ -868,10 +856,10 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
@@ -883,10 +871,10 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="8" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
         <v>32</v>
@@ -894,10 +882,10 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="8" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
@@ -991,7 +979,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D73A0C9-9802-0C4C-A2B3-372B9ED806BE}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -1016,13 +1004,13 @@
         <v>73</v>
       </c>
       <c r="B2" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1030,27 +1018,13 @@
         <v>74</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/models/downapikey.xlsx
+++ b/models/downapikey.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ymq/py/dapi/models/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78676F20-4C8D-5F43-9AB2-DA5E2AC622E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94C97B51-ABB9-D54C-BB60-82D75200193D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19240" yWindow="5760" windowWidth="40920" windowHeight="24580" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="summary" sheetId="1" r:id="rId1"/>
@@ -865,7 +865,7 @@
         <v>10</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="F5" s="7"/>
     </row>
@@ -897,7 +897,7 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>coding!$B$2:$B$12</xm:f>
